--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486883_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486883_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.99</v>
+        <v>6.4116</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1136</v>
+        <v>6.1795</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1236</v>
+        <v>0.2321</v>
       </c>
       <c r="G2" t="n">
         <v>2.9237</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2449</v>
+        <v>0.6664</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1467</v>
+        <v>1.2125</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9018</v>
+        <v>-0.5461</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1846</v>
+        <v>3.2736</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4195</v>
+        <v>1.7209</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7651</v>
+        <v>1.5527</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4474</v>
+        <v>2.6937</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9083</v>
+        <v>1.9466</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5391</v>
+        <v>0.7472</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6521</v>
+        <v>3.8058</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6263</v>
+        <v>2.1091</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0257</v>
+        <v>1.6967</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2047</v>
+        <v>-1.1121</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2819</v>
+        <v>-0.1626</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4866</v>
+        <v>-0.9495</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2053</v>
+        <v>-2.4641</v>
       </c>
       <c r="R3" t="n">
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3162</v>
+        <v>0.6538</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0272</v>
+        <v>0.2478</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2889</v>
+        <v>0.406</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1314</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1314</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6193</v>
+        <v>2.9507</v>
       </c>
       <c r="E4" t="n">
-        <v>1.497</v>
+        <v>1.0669</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1223</v>
+        <v>1.8837</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3239</v>
+        <v>1.4474</v>
       </c>
       <c r="H4" t="n">
-        <v>2.826</v>
+        <v>0.9083</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.502</v>
+        <v>0.5391</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4413</v>
+        <v>1.6521</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2045</v>
+        <v>0.6263</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2368</v>
+        <v>1.0257</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1173</v>
+        <v>-0.2047</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6215</v>
+        <v>0.2819</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7388</v>
+        <v>-0.4866</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.2321</v>
+        <v>2.0534</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4908</v>
+        <v>-0.2053</v>
       </c>
       <c r="R4" t="n">
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5192</v>
+        <v>-0.5502</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9491000000000001</v>
+        <v>-0.3798</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4298</v>
+        <v>-0.1704</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5559</v>
+        <v>2.6852</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4914</v>
+        <v>1.5629</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0645</v>
+        <v>1.1223</v>
       </c>
       <c r="G5" t="n">
-        <v>0.579</v>
+        <v>1.3239</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7104</v>
+        <v>2.826</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1314</v>
+        <v>-1.502</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4964</v>
+        <v>1.4413</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2599</v>
+        <v>1.2045</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2365</v>
+        <v>0.2368</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9174</v>
+        <v>-0.1173</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4505</v>
+        <v>1.6215</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3679</v>
+        <v>-1.7388</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>-3.4908</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>2.2588</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8805</v>
+        <v>0.5851</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7117</v>
+        <v>1.0149</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1687</v>
+        <v>-0.4298</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6982</v>
+        <v>2.0082</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4579</v>
+        <v>2.5975</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5505</v>
+        <v>1.8197</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0274</v>
+        <v>2.7359</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5231</v>
+        <v>-0.9162</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6937</v>
+        <v>1.0827</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9466</v>
+        <v>0.5091</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7472</v>
+        <v>0.5736</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8058</v>
+        <v>2.3081</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1091</v>
+        <v>-0.1912</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6967</v>
+        <v>2.4994</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1121</v>
+        <v>-1.2254</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1626</v>
+        <v>0.7004</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9495</v>
+        <v>-1.9258</v>
       </c>
       <c r="P6" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4641</v>
+        <v>-2.2588</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0693</v>
+        <v>0.004</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4457</v>
+        <v>0.3293</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3764</v>
+        <v>-0.3253</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1314</v>
+        <v>0.9384</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1314</v>
+        <v>2.3573</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0429</v>
+        <v>0.8658</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8405</v>
+        <v>-0.0505</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7976</v>
+        <v>0.9163</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0827</v>
+        <v>0.579</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5091</v>
+        <v>0.7104</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5736</v>
+        <v>-0.1314</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3081</v>
+        <v>1.4964</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1912</v>
+        <v>0.2599</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4994</v>
+        <v>1.2365</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2254</v>
+        <v>-0.9174</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7004</v>
+        <v>0.4505</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9258</v>
+        <v>-1.3679</v>
       </c>
       <c r="P7" t="n">
         <v>-0.2053</v>
@@ -1000,28 +1000,28 @@
         <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2271</v>
+        <v>1.1904</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4339</v>
+        <v>1.1698</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2067</v>
+        <v>0.0205</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9384</v>
+        <v>-0.6982</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3573</v>
+        <v>-0.4579</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2422</v>
+        <v>0.1732</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1117</v>
+        <v>-0.1175</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3539</v>
+        <v>0.2907</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0755</v>
+        <v>-0.5376</v>
       </c>
       <c r="H8" t="n">
-        <v>0.182</v>
+        <v>3.5197</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2575</v>
+        <v>-4.0573</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8105</v>
+        <v>1.1139</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6526</v>
+        <v>2.4561</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1579</v>
+        <v>-1.3422</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.886</v>
+        <v>-1.6515</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4706</v>
+        <v>1.0636</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4154</v>
+        <v>-2.7151</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4963</v>
+        <v>-0.0571</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1045</v>
+        <v>0.6701</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3918</v>
+        <v>-0.7272</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BALADA SEGOVIA</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6965</v>
+        <v>-0.1679</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7902</v>
+        <v>-0.2551</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0871</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8899</v>
+        <v>-1.0755</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5968</v>
+        <v>0.182</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4867</v>
+        <v>-1.2575</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6584</v>
+        <v>0.8105</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0389</v>
+        <v>0.6526</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6974</v>
+        <v>0.1579</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2314</v>
+        <v>-1.886</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5579</v>
+        <v>-0.4706</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7893</v>
+        <v>-1.4154</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1208</v>
+        <v>0.0862</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>-0.0388</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0109</v>
+        <v>0.125</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>A. BALADA SEGOVIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2368</v>
+        <v>-0.3374</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4386</v>
+        <v>-0.3718</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2018</v>
+        <v>0.0344</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5376</v>
+        <v>-0.8899</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5197</v>
+        <v>0.5968</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0573</v>
+        <v>-1.4867</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1139</v>
+        <v>-0.6584</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4561</v>
+        <v>0.0389</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3422</v>
+        <v>-0.6974</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6515</v>
+        <v>-0.2314</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0636</v>
+        <v>0.5579</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.7151</v>
+        <v>-0.7893</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6694</v>
+        <v>0.2053</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4672</v>
+        <v>0.2383</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.651</v>
+        <v>0.2867</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8162</v>
+        <v>-0.0484</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1786</v>
+        <v>0.1088</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3272</v>
+        <v>-2.0909</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8798</v>
+        <v>-0.6435</v>
       </c>
       <c r="F11" t="n">
         <v>-1.4474</v>
@@ -1312,10 +1312,10 @@
         <v>3.0801</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7864</v>
+        <v>-0.5501</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2171</v>
+        <v>0.0192</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5693</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.9249</v>
+        <v>15.5836</v>
       </c>
       <c r="E12" t="n">
-        <v>11.1691</v>
+        <v>11.8277</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7558</v>
+        <v>3.7557</v>
       </c>
       <c r="G12" t="n">
         <v>6.721100000000001</v>
@@ -1369,7 +1369,7 @@
         <v>10.9521</v>
       </c>
       <c r="L12" t="n">
-        <v>5.785900000000002</v>
+        <v>5.785900000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-10.0167</v>
@@ -1390,19 +1390,19 @@
         <v>20.5342</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6081</v>
+        <v>2.2668</v>
       </c>
       <c r="T12" t="n">
-        <v>3.873200000000001</v>
+        <v>4.531699999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2649</v>
+        <v>-2.265</v>
       </c>
       <c r="V12" t="n">
-        <v>2.488500000000001</v>
+        <v>2.4885</v>
       </c>
       <c r="W12" t="n">
-        <v>6.985500000000001</v>
+        <v>6.9855</v>
       </c>
       <c r="X12" t="n">
         <v>-4.4969</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2079</v>
+        <v>6.8903</v>
       </c>
       <c r="E13" t="n">
-        <v>7.134</v>
+        <v>8.389200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.926</v>
+        <v>-1.4989</v>
       </c>
       <c r="G13" t="n">
         <v>10.3566</v>
@@ -1468,13 +1468,13 @@
         <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7647</v>
+        <v>-0.0823</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9804</v>
+        <v>0.2749</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7844</v>
+        <v>-0.3572</v>
       </c>
       <c r="V13" t="n">
         <v>-2.3573</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7049</v>
+        <v>0.0848</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4151</v>
+        <v>0.6813</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2898</v>
+        <v>-0.5965</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7266</v>
+        <v>-2.2055</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7136</v>
+        <v>-1.953</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.013</v>
+        <v>-0.2525</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0045</v>
+        <v>-0.5011</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0789</v>
+        <v>0.1184</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7311</v>
+        <v>-1.7044</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6392</v>
+        <v>-1.3335</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.092</v>
+        <v>-0.3709</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6636</v>
+        <v>0.0377</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1971</v>
+        <v>0.2091</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4666</v>
+        <v>-0.1714</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5893</v>
+        <v>1.6366</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3491</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3075</v>
+        <v>-0.2051</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5767</v>
+        <v>-0.3171</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8842</v>
+        <v>0.112</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.2055</v>
+        <v>-0.7266</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.953</v>
+        <v>-0.7136</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2525</v>
+        <v>-0.013</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5011</v>
+        <v>0.0045</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1184</v>
+        <v>0.0789</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7044</v>
+        <v>-0.7311</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3335</v>
+        <v>-0.6392</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3709</v>
+        <v>-0.092</v>
       </c>
       <c r="P15" t="n">
-        <v>0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3546</v>
+        <v>0.7536</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1045</v>
+        <v>0.4649</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4591</v>
+        <v>0.2887</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6366</v>
+        <v>0.5893</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4579</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4246</v>
+        <v>-0.3706</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6694</v>
+        <v>-1.9832</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2447</v>
+        <v>1.6126</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2626</v>
@@ -1702,13 +1702,13 @@
         <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2219</v>
+        <v>0.276</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1117</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8898</v>
+        <v>-0.5219</v>
       </c>
       <c r="V16" t="n">
         <v>0.5893</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2904</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1895</v>
+        <v>0.6079</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4799</v>
+        <v>-1.2899</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2543</v>
@@ -1780,13 +1780,13 @@
         <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0279</v>
+        <v>-0.4194</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3489</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.679</v>
+        <v>-0.489</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8295</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1282</v>
+        <v>-1.5168</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5568</v>
+        <v>-1.5646</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5714</v>
+        <v>0.0478</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2286</v>
+        <v>-1.4955</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.052</v>
+        <v>-3.0848</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1766</v>
+        <v>1.5894</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8567</v>
+        <v>-0.3673</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8048999999999999</v>
+        <v>-2.4196</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0518</v>
+        <v>2.0522</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0853</v>
+        <v>-1.1281</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8569</v>
+        <v>-0.6653</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2284</v>
+        <v>-0.4629</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4374</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2855</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4622</v>
+        <v>-0.0213</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2826</v>
+        <v>0.0348</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7448</v>
+        <v>-0.0561</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1618</v>
+        <v>-2.252</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2944</v>
+        <v>-0.8706</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.4562</v>
+        <v>-1.3814</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0065</v>
+        <v>-0.2286</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0437</v>
+        <v>-0.052</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0372</v>
+        <v>-0.1766</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8022</v>
+        <v>1.8567</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1844</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9866</v>
+        <v>1.0518</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8088</v>
+        <v>-2.0853</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8593</v>
+        <v>-0.8569</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9495</v>
+        <v>-1.2284</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2053</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2588</v>
+        <v>-3.2855</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4641</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9967</v>
+        <v>-0.586</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5723</v>
+        <v>-0.0312</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5756</v>
+        <v>-0.5548</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.5359</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3223</v>
+        <v>-2.9202</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1922</v>
+        <v>-1.9852</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.13</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4955</v>
+        <v>-2.7555</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.0848</v>
+        <v>-1.0056</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5894</v>
+        <v>-1.7499</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3673</v>
+        <v>-1.7217</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4196</v>
+        <v>-0.3664</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0522</v>
+        <v>-1.3552</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1281</v>
+        <v>-1.0338</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6653</v>
+        <v>-0.6392</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4629</v>
+        <v>-0.3947</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8268</v>
+        <v>-0.1647</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5928</v>
+        <v>-0.2635</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.234</v>
+        <v>0.0988</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9795</v>
+        <v>-3.4031</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9852</v>
+        <v>0.9345</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9943</v>
+        <v>-4.3376</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7555</v>
+        <v>-2.0065</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0056</v>
+        <v>-2.0437</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7499</v>
+        <v>0.0372</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7217</v>
+        <v>0.8022</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3664</v>
+        <v>-0.1844</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3552</v>
+        <v>0.9866</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0338</v>
+        <v>-2.8088</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6392</v>
+        <v>-1.8593</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3947</v>
+        <v>-0.9495</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4641</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.224</v>
+        <v>0.7554</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2635</v>
+        <v>1.2124</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0395</v>
+        <v>-0.457</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.5359</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8183</v>
+        <v>-3.7521</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9466</v>
+        <v>-2.842</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8717</v>
+        <v>-0.9101</v>
       </c>
       <c r="G22" t="n">
         <v>-1.169</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6842</v>
+        <v>-0.618</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.527</v>
+        <v>-0.4224</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1572</v>
+        <v>-0.1956</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9384</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4052</v>
+        <v>-5.4034</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0152</v>
+        <v>-4.806</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3899</v>
+        <v>-0.5974</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9736</v>
@@ -2248,13 +2248,13 @@
         <v>1.8481</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1461</v>
+        <v>-0.1443</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2907</v>
+        <v>-0.0815</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1447</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.1786</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.925</v>
+        <v>-13.5302</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7557</v>
+        <v>-3.7558</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.1691</v>
+        <v>-9.7744</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.721099999999998</v>
+        <v>-6.721100000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-16.7064</v>
       </c>
       <c r="I24" t="n">
-        <v>9.985399999999997</v>
+        <v>9.9854</v>
       </c>
       <c r="J24" t="n">
         <v>10.0168</v>
@@ -2326,13 +2326,13 @@
         <v>16.4274</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6083</v>
+        <v>-0.2132999999999997</v>
       </c>
       <c r="T24" t="n">
         <v>2.264899999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.8731</v>
+        <v>-2.4783</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4887</v>
